--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.37838</v>
+        <v>17.30161</v>
       </c>
       <c r="D2" t="n">
-        <v>17.40331</v>
+        <v>17.19563</v>
       </c>
       <c r="E2" t="n">
-        <v>17.12604</v>
+        <v>17.27092</v>
       </c>
       <c r="F2" t="n">
-        <v>43.2257</v>
+        <v>42.9416</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05241</v>
+        <v>0.05067</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91614</v>
+        <v>1.90294</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.57705</v>
+        <v>17.29916</v>
       </c>
       <c r="D3" t="n">
-        <v>17.3095</v>
+        <v>16.80596</v>
       </c>
       <c r="E3" t="n">
-        <v>17.18109</v>
+        <v>16.90938</v>
       </c>
       <c r="F3" t="n">
-        <v>43.09016</v>
+        <v>43.86705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05268</v>
+        <v>0.0519</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85275</v>
+        <v>1.87084</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.00577</v>
+        <v>17.31987</v>
       </c>
       <c r="D4" t="n">
-        <v>17.16704</v>
+        <v>17.14763</v>
       </c>
       <c r="E4" t="n">
-        <v>17.13448</v>
+        <v>17.24878</v>
       </c>
       <c r="F4" t="n">
-        <v>44.07627</v>
+        <v>43.64094</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05211</v>
+        <v>0.05206</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84413</v>
+        <v>1.89374</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.12191</v>
+        <v>17.14147</v>
       </c>
       <c r="D6" t="n">
-        <v>16.48199</v>
+        <v>16.49908</v>
       </c>
       <c r="E6" t="n">
-        <v>17.11741</v>
+        <v>16.71231</v>
       </c>
       <c r="F6" t="n">
-        <v>22.19729</v>
+        <v>22.40088</v>
       </c>
       <c r="G6" t="n">
-        <v>34.7051</v>
+        <v>35.10172</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.40966</v>
+        <v>17.04322</v>
       </c>
       <c r="D7" t="n">
-        <v>16.37033</v>
+        <v>16.43006</v>
       </c>
       <c r="E7" t="n">
-        <v>17.40162</v>
+        <v>16.79444</v>
       </c>
       <c r="F7" t="n">
-        <v>22.70779</v>
+        <v>22.40438</v>
       </c>
       <c r="G7" t="n">
-        <v>35.39097</v>
+        <v>34.53532</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.08507</v>
+        <v>17.27698</v>
       </c>
       <c r="D8" t="n">
-        <v>16.48194</v>
+        <v>16.37366</v>
       </c>
       <c r="E8" t="n">
-        <v>16.98451</v>
+        <v>16.79913</v>
       </c>
       <c r="F8" t="n">
-        <v>22.05192</v>
+        <v>22.2133</v>
       </c>
       <c r="G8" t="n">
-        <v>35.21945</v>
+        <v>35.22486</v>
       </c>
     </row>
   </sheetData>
